--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/40_CYBERSECURITY/valcanary_poam_register_q4_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/40_CYBERSECURITY/valcanary_poam_register_q4_2024.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
